--- a/v1.2.0/意图识别说明-v1.2.0.xlsx
+++ b/v1.2.0/意图识别说明-v1.2.0.xlsx
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>SKU=AC380V</t>
+          <t>规格=AC380V</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>SKU=AC380V</t>
+          <t>规格=AC380V</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
